--- a/HSI_FSC_result/2. Dropout/score_basic.xlsx
+++ b/HSI_FSC_result/2. Dropout/score_basic.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_0_basic\result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_result\2. Dropout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB67040E-6A37-45EA-BAE8-2BF07ADA3726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95678DB-9CC7-4C22-893F-A4848780F5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5100" yWindow="1920" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5955" yWindow="2670" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IP" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -67,6 +67,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -80,10 +92,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -364,17 +378,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>40</v>
       </c>
       <c r="B1">
         <v>49.45055</v>
       </c>
-      <c r="C1">
+      <c r="C1" s="4">
         <v>19.409282999999999</v>
       </c>
       <c r="D1">
@@ -405,15 +419,19 @@
         <f>AVERAGE(A1:K1)</f>
         <v>31.844011909090909</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1">
+        <f>MAX(A1:K1)</f>
+        <v>49.45055</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>44.220730000000003</v>
       </c>
       <c r="B2">
         <v>56.331879999999998</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="4">
         <v>37.594799999999999</v>
       </c>
       <c r="D2">
@@ -444,15 +462,19 @@
         <f t="shared" ref="L2:L19" si="0">AVERAGE(A2:K2)</f>
         <v>46.36256854545455</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M2">
+        <f t="shared" ref="M2:M19" si="1">MAX(A2:K2)</f>
+        <v>72.164950000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>31.520223999999999</v>
       </c>
       <c r="B3">
         <v>46.875</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="4">
         <v>39.181286</v>
       </c>
       <c r="D3">
@@ -483,15 +505,19 @@
         <f t="shared" si="0"/>
         <v>34.417541454545464</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M3">
+        <f t="shared" si="1"/>
+        <v>46.875</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>69.938643999999996</v>
       </c>
       <c r="B4">
         <v>25.748502999999999</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="4">
         <v>48.314605999999998</v>
       </c>
       <c r="D4">
@@ -522,15 +548,19 @@
         <f t="shared" si="0"/>
         <v>38.353631999999998</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M4">
+        <f t="shared" si="1"/>
+        <v>69.938643999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>60.224716000000001</v>
       </c>
       <c r="B5">
         <v>54.491019999999999</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="4">
         <v>76.231260000000006</v>
       </c>
       <c r="D5">
@@ -561,15 +591,19 @@
         <f t="shared" si="0"/>
         <v>57.427013454545452</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M5">
+        <f t="shared" si="1"/>
+        <v>79.827089999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>95.409180000000006</v>
       </c>
       <c r="B6">
         <v>99.149665999999996</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="4">
         <v>100</v>
       </c>
       <c r="D6">
@@ -600,15 +634,19 @@
         <f t="shared" si="0"/>
         <v>94.409387818181827</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M6">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>8.6687309999999993</v>
       </c>
       <c r="B7">
         <v>18.064516000000001</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="4">
         <v>22.400002000000001</v>
       </c>
       <c r="D7">
@@ -639,15 +677,19 @@
         <f t="shared" si="0"/>
         <v>28.967268181818181</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M7">
+        <f t="shared" si="1"/>
+        <v>93.333336000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>88.490560000000002</v>
       </c>
       <c r="B8">
         <v>96.957404999999994</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="4">
         <v>100</v>
       </c>
       <c r="D8">
@@ -678,15 +720,19 @@
         <f t="shared" si="0"/>
         <v>89.039125999999996</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M8">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>11.173183999999999</v>
       </c>
       <c r="B9">
         <v>54.285716999999998</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="4">
         <v>57.142859999999999</v>
       </c>
       <c r="D9">
@@ -717,15 +763,19 @@
         <f t="shared" si="0"/>
         <v>25.004091727272733</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M9">
+        <f t="shared" si="1"/>
+        <v>57.142859999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>61.649940000000001</v>
       </c>
       <c r="B10">
         <v>28.518518</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="4">
         <v>44.279944999999998</v>
       </c>
       <c r="D10">
@@ -756,15 +806,19 @@
         <f t="shared" si="0"/>
         <v>39.336775272727273</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M10">
+        <f t="shared" si="1"/>
+        <v>71.890144000000006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>70.784030000000001</v>
       </c>
       <c r="B11">
         <v>52.649009999999997</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="4">
         <v>70.773809999999997</v>
       </c>
       <c r="D11">
@@ -795,15 +849,19 @@
         <f t="shared" si="0"/>
         <v>63.772725727272729</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M11">
+        <f t="shared" si="1"/>
+        <v>78.383026000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>32.778489999999998</v>
       </c>
       <c r="B12">
         <v>41.306640000000002</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="4">
         <v>55.334282000000002</v>
       </c>
       <c r="D12">
@@ -834,15 +892,19 @@
         <f t="shared" si="0"/>
         <v>35.406395272727281</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M12">
+        <f t="shared" si="1"/>
+        <v>55.334282000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>82.448975000000004</v>
       </c>
       <c r="B13">
         <v>84.482759999999999</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="4">
         <v>31.336407000000001</v>
       </c>
       <c r="D13">
@@ -873,15 +935,19 @@
         <f t="shared" si="0"/>
         <v>66.665082727272718</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M13">
+        <f t="shared" si="1"/>
+        <v>96.984924000000007</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>89.482069999999993</v>
       </c>
       <c r="B14">
         <v>92.223330000000004</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="4">
         <v>98.180160000000001</v>
       </c>
       <c r="D14">
@@ -912,15 +978,19 @@
         <f t="shared" si="0"/>
         <v>89.626471818181798</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M14">
+        <f t="shared" si="1"/>
+        <v>98.180160000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>59.203983000000001</v>
       </c>
       <c r="B15">
         <v>68.733153999999999</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="4">
         <v>72.580650000000006</v>
       </c>
       <c r="D15">
@@ -951,15 +1021,19 @@
         <f t="shared" si="0"/>
         <v>59.075346545454543</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M15">
+        <f t="shared" si="1"/>
+        <v>72.580650000000006</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>75.609759999999994</v>
       </c>
       <c r="B16">
         <v>32.5</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="4">
         <v>33.955227000000001</v>
       </c>
       <c r="D16">
@@ -990,15 +1064,19 @@
         <f t="shared" si="0"/>
         <v>41.755500545454545</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M16">
+        <f t="shared" si="1"/>
+        <v>75.609759999999994</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>58.581325007317702</v>
       </c>
       <c r="B17">
         <v>54.024782905649303</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="4">
         <v>59.927797833935003</v>
       </c>
       <c r="D17">
@@ -1029,15 +1107,19 @@
         <f t="shared" si="0"/>
         <v>53.724088381128041</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="M17">
+        <f t="shared" si="1"/>
+        <v>59.927797833935003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
         <v>57.600200176238999</v>
       </c>
       <c r="B18">
         <v>56.3604831695556</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="4">
         <v>56.66965842247</v>
       </c>
       <c r="D18">
@@ -1068,15 +1150,19 @@
         <f t="shared" si="0"/>
         <v>52.591433850201632</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M18">
+        <f t="shared" si="1"/>
+        <v>57.600200176238999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>53.984732202108297</v>
       </c>
       <c r="B19">
         <v>49.482937786945101</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="4">
         <v>55.248530800197003</v>
       </c>
       <c r="D19">
@@ -1107,6 +1193,16 @@
         <f t="shared" si="0"/>
         <v>48.784211841267144</v>
       </c>
+      <c r="M19">
+        <f t="shared" si="1"/>
+        <v>55.248530800197003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C21" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1768,7 +1864,7 @@
       <c r="H17">
         <v>87.448502651074193</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="4">
         <v>91.263463208261697</v>
       </c>
       <c r="J17">
@@ -1777,7 +1873,7 @@
       <c r="K17">
         <v>87.6905170980435</v>
       </c>
-      <c r="L17" s="1">
+      <c r="L17" s="4">
         <f t="shared" si="0"/>
         <v>86.86672746418904</v>
       </c>
@@ -1807,7 +1903,7 @@
       <c r="H18">
         <v>91.793966293334904</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="4">
         <v>94.712436199188204</v>
       </c>
       <c r="J18">
@@ -1816,7 +1912,7 @@
       <c r="K18">
         <v>92.986714839935303</v>
       </c>
-      <c r="L18" s="1">
+      <c r="L18" s="4">
         <f t="shared" si="0"/>
         <v>90.425407344644682</v>
       </c>
@@ -1846,7 +1942,7 @@
       <c r="H19">
         <v>86.014396136871497</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="4">
         <v>90.287160068846404</v>
       </c>
       <c r="J19">
@@ -1855,7 +1951,7 @@
       <c r="K19">
         <v>86.391414346230903</v>
       </c>
-      <c r="L19" s="1">
+      <c r="L19" s="4">
         <f t="shared" si="0"/>
         <v>85.438886472888456</v>
       </c>
@@ -2240,7 +2336,7 @@
       <c r="F10">
         <v>74.289321114643698</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="4">
         <v>80.463343931176297</v>
       </c>
       <c r="H10">
@@ -2279,7 +2375,7 @@
       <c r="F11">
         <v>69.947004318237305</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="4">
         <v>77.608227729797306</v>
       </c>
       <c r="H11">
@@ -2318,7 +2414,7 @@
       <c r="F12">
         <v>66.7560625173424</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="4">
         <v>74.223639692254807</v>
       </c>
       <c r="H12">
